--- a/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260625.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260625.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D71"/>
+  <dimension ref="A1:D72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>35,061</t>
+          <t>34,835</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>10.52%</t>
+          <t>10.62%</t>
         </is>
       </c>
     </row>
@@ -633,12 +633,12 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>84,749</t>
+          <t>84,203</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>9.73%</t>
+          <t>9.93%</t>
         </is>
       </c>
     </row>
@@ -655,12 +655,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>97,756</t>
+          <t>97,127</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>8.78%</t>
+          <t>8.88%</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>38,480</t>
+          <t>38,232</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>7.66%</t>
+          <t>7.72%</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>211,210</t>
+          <t>209,850</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.25%</t>
+          <t>5.17%</t>
         </is>
       </c>
     </row>
@@ -721,12 +721,12 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>53,026</t>
+          <t>52,684</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.91%</t>
+          <t>4.57%</t>
         </is>
       </c>
     </row>
@@ -743,12 +743,12 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>112,330</t>
+          <t>111,607</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>4.03%</t>
+          <t>3.98%</t>
         </is>
       </c>
     </row>
@@ -765,12 +765,12 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>121,826</t>
+          <t>121,042</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.31%</t>
+          <t>3.26%</t>
         </is>
       </c>
     </row>
@@ -787,12 +787,12 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>20,973</t>
+          <t>20,838</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.08%</t>
+          <t>3.14%</t>
         </is>
       </c>
     </row>
@@ -809,12 +809,12 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>63,809</t>
+          <t>63,398</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.03%</t>
+          <t>3.06%</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>126,715</t>
+          <t>125,899</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.49%</t>
+          <t>2.46%</t>
         </is>
       </c>
     </row>
@@ -853,12 +853,12 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>58,688</t>
+          <t>58,310</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.25%</t>
+          <t>2.24%</t>
         </is>
       </c>
     </row>
@@ -875,56 +875,56 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>147,514</t>
+          <t>146,564</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>1.96%</t>
+          <t>1.92%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>FSLR US</t>
+          <t>CEG US</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>第一太陽能</t>
+          <t>星座能源公司</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>26,303</t>
+          <t>24,228</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>1.85%</t>
+          <t>1.83%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>CEG US</t>
+          <t>FSLR US</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>星座能源公司</t>
+          <t>第一太陽能</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>24,385</t>
+          <t>26,133</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.85%</t>
+          <t>1.82%</t>
         </is>
       </c>
     </row>
@@ -941,12 +941,12 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>67,428</t>
+          <t>66,994</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.56%</t>
+          <t>1.54%</t>
         </is>
       </c>
     </row>
@@ -963,56 +963,56 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>12,270</t>
+          <t>12,191</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.37%</t>
+          <t>1.38%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>ED US</t>
+          <t>PEG US</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>聯合愛迪生</t>
+          <t>大眾服務企業集團公司</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>39,805</t>
+          <t>53,481</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.25%</t>
+          <t>1.24%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>PEG US</t>
+          <t>ED US</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>大眾服務企業集團公司</t>
+          <t>聯合愛迪生</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>53,828</t>
+          <t>39,549</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.25%</t>
+          <t>1.23%</t>
         </is>
       </c>
     </row>
@@ -1029,12 +1029,12 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>55,423</t>
+          <t>55,066</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.17%</t>
+          <t>1.16%</t>
         </is>
       </c>
     </row>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>35,185</t>
+          <t>34,958</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -1063,17 +1063,17 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>FE US</t>
+          <t>VST US</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>第一能源公司</t>
+          <t>維斯達能源公司</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>83,336</t>
+          <t>23,934</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -1085,44 +1085,44 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>AGX US</t>
+          <t>FE US</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>阿根公司</t>
+          <t>第一能源公司</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>5,326</t>
+          <t>82,799</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.11%</t>
+          <t>1.12%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>VST US</t>
+          <t>AGX US</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>維斯達能源公司</t>
+          <t>阿根公司</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>24,089</t>
+          <t>5,292</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.11%</t>
+          <t>1.12%</t>
         </is>
       </c>
     </row>
@@ -1139,12 +1139,12 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>54,178</t>
+          <t>53,829</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.10%</t>
+          <t>1.09%</t>
         </is>
       </c>
     </row>
@@ -1161,73 +1161,73 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>32,949</t>
+          <t>32,737</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.07%</t>
+          <t>1.06%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>ACM UN</t>
+          <t>AEIS US</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>艾奕康</t>
+          <t>艾儀有限公司</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>50,896</t>
+          <t>9,682</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.01%</t>
+          <t>1.02%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>AEIS US</t>
+          <t>ACM UN</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>艾儀有限公司</t>
+          <t>艾奕康</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>9,745</t>
+          <t>50,568</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.99%</t>
+          <t>1.00%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>AEE US</t>
+          <t>DTE US</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>阿莫林公司</t>
+          <t>DTE能源</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>29,837</t>
+          <t>22,268</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -1239,22 +1239,22 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>DTE US</t>
+          <t>AEE US</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>DTE能源</t>
+          <t>阿莫林公司</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>22,413</t>
+          <t>29,645</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.96%</t>
+          <t>0.95%</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>11,522</t>
+          <t>11,448</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.93%</t>
+          <t>0.95%</t>
         </is>
       </c>
     </row>
@@ -1293,12 +1293,12 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>14,343</t>
+          <t>14,250</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.89%</t>
+          <t>0.91%</t>
         </is>
       </c>
     </row>
@@ -1315,12 +1315,12 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>81,250</t>
+          <t>80,727</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.85%</t>
+          <t>0.84%</t>
         </is>
       </c>
     </row>
@@ -1337,12 +1337,12 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>102,884</t>
+          <t>102,221</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.83%</t>
+          <t>0.82%</t>
         </is>
       </c>
     </row>
@@ -1359,12 +1359,12 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>32,808</t>
+          <t>32,597</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.80%</t>
+          <t>0.79%</t>
         </is>
       </c>
     </row>
@@ -1381,12 +1381,12 @@
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>157,951</t>
+          <t>156,934</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.77%</t>
+          <t>0.75%</t>
         </is>
       </c>
     </row>
@@ -1403,73 +1403,73 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>33,216</t>
+          <t>33,002</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.72%</t>
+          <t>0.71%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>202609ESU6</t>
+          <t>POWL US</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>小型S＆P 500股價指數</t>
+          <t>Powell工業公司</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7,341</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>0.63%</t>
+          <t>0.64%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>POWL US</t>
+          <t>202609ESU6</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>Powell工業公司</t>
+          <t>小型S＆P 500股價指數</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>7,389</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>0.62%</t>
+          <t>0.63%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>LNT US</t>
+          <t>NRG US</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>聯合能源公司</t>
+          <t>NRG Energy Inc</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>27,902</t>
+          <t>14,434</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -1481,17 +1481,17 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>CNP US</t>
+          <t>LNT US</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>Centerpoint能源</t>
+          <t>聯合能源公司</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>47,061</t>
+          <t>27,722</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -1503,17 +1503,17 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>NRG US</t>
+          <t>VICR US</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>NRG Energy Inc</t>
+          <t>懷克爾公司</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>14,528</t>
+          <t>6,320</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -1525,17 +1525,17 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>VICR US</t>
+          <t>CNP US</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>懷克爾公司</t>
+          <t>Centerpoint能源</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>6,361</t>
+          <t>46,758</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -1557,12 +1557,12 @@
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>3,951</t>
+          <t>3,926</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>0.53%</t>
+          <t>0.54%</t>
         </is>
       </c>
     </row>
@@ -1579,7 +1579,7 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>17,454</t>
+          <t>17,342</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>102,276</t>
+          <t>101,617</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>0.42%</t>
         </is>
       </c>
     </row>
@@ -1623,12 +1623,12 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>25,454</t>
+          <t>25,290</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>0.34%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>3,073</t>
+          <t>3,053</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>0.26%</t>
+          <t>0.27%</t>
         </is>
       </c>
     </row>
@@ -1667,7 +1667,7 @@
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>8,681</t>
+          <t>8,625</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>19,971</t>
+          <t>19,842</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>41,408</t>
+          <t>41,142</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -1719,6 +1719,20 @@
           <t>0.01%</t>
         </is>
       </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>C_NTD</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr"/>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>123,025,739</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="5">
